--- a/Hoadon/HDRa/7/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/7/Hoadondientu.xlsx
@@ -314,6 +314,89 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25THV</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>01/07/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3500100110</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>VIỄN THÔNG BÀ RỊA -VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Số 35 đường 3/2, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>1.8E7</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>1800000.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>1.98E7</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>

--- a/Hoadon/HDRa/7/Hoadondientu.xlsx
+++ b/Hoadon/HDRa/7/Hoadondientu.xlsx
@@ -314,6 +314,89 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>C25TNT</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>29/07/2025</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>3502267355</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG NGỌC TRÂN</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0303765858</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG SONG HÂN</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>36/21 Đường D2, Phường Thạnh Mỹ Tây, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>3.834E8</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>3.0672E7</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>4.14072E8</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Đã cấp mã hóa đơn</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
